--- a/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_e_mediabrut_a_2021.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_e_mediabrut_a_2021.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:21</t>
+    <t xml:space="preserve">2026-09-24 01:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -637,10 +637,10 @@
         <v>16</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>-0.09</v>
+        <v>0.06</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="11">
@@ -651,10 +651,10 @@
         <v>16</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>0.03</v>
+        <v>0.14</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="12">
@@ -665,10 +665,10 @@
         <v>16</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="13">
@@ -679,10 +679,10 @@
         <v>16</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>-0.13</v>
+        <v>-0.08</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="14">
@@ -707,10 +707,10 @@
         <v>22</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>0.1</v>
+        <v>0.58</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="16">
@@ -721,10 +721,10 @@
         <v>22</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>0</v>
+        <v>-0.46</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="17">
@@ -738,7 +738,7 @@
         <v>-0.03</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="18">
